--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:29:24+00:00</t>
+    <t>2026-09-02T07:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:15:34+00:00</t>
+    <t>2026-09-02T11:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:58:19+00:00</t>
+    <t>2026-09-02T12:35:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:35:29+00:00</t>
+    <t>2026-09-02T13:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:00:33+00:00</t>
+    <t>2026-09-02T15:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:34:02+00:00</t>
+    <t>2026-09-02T17:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:45:23+00:00</t>
+    <t>2026-09-02T17:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:09+00:00</t>
+    <t>2026-09-02T18:06:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1176,76 +1176,72 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:coding}
+</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category.id</t>
+  </si>
+  <si>
+    <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category.text</t>
+  </si>
+  <si>
+    <t>Observation.category:laboruntersuchung</t>
+  </si>
+  <si>
+    <t>laboruntersuchung</t>
+  </si>
+  <si>
+    <t>Laboruntersuchungs-Kategorie</t>
+  </si>
+  <si>
+    <t>Die verpflichtende Kategorie der Laboruntersuchung. Weitere Kategorien, etwa der Laborbereich, sind als zusaetzliche category-Eintraege zulaessig.</t>
+  </si>
+  <si>
+    <t>Observation.category:laboruntersuchung.id</t>
+  </si>
+  <si>
+    <t>Observation.category:laboruntersuchung.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:laboruntersuchung.coding</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">pattern:$this}
 </t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t>Observation.category.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category.text</t>
-  </si>
-  <si>
-    <t>Observation.category:laboruntersuchung</t>
-  </si>
-  <si>
-    <t>laboruntersuchung</t>
-  </si>
-  <si>
-    <t>Laboruntersuchungs-Kategorie</t>
-  </si>
-  <si>
-    <t>Die verpflichtende Kategorie der Laboruntersuchung. Weitere Kategorien, etwa der Laborbereich, sind als zusaetzliche category-Eintraege zulaessig.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="26436-6"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.category:laboruntersuchung.id</t>
-  </si>
-  <si>
-    <t>Observation.category:laboruntersuchung.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:laboruntersuchung.coding</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Observation.category:laboruntersuchung.coding.id</t>
@@ -9560,7 +9556,7 @@
         <v>82</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>82</v>
@@ -9631,7 +9627,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>375</v>
@@ -9746,7 +9742,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>376</v>
@@ -9863,7 +9859,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>377</v>
@@ -9874,7 +9870,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>81</v>
@@ -9938,7 +9934,7 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
@@ -11588,7 +11584,7 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="AC74" s="2"/>
       <c r="AD74" t="s" s="2">

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T20:13:51+00:00</t>
+    <t>2026-09-08T09:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:04+00:00</t>
+    <t>2026-09-08T11:22:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:22:39+00:00</t>
+    <t>2026-09-08T11:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
